--- a/Example/【必读】例程功能说明.xlsx
+++ b/Example/【必读】例程功能说明.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1AC46DD-87BD-4A7F-A64F-43A5F3D8C340}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A137758-0895-4106-9EE3-4BABE2120C64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="29025" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5595" yWindow="4380" windowWidth="24090" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="164">
   <si>
     <t>文件夹名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -288,10 +288,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E8_camera（小钻风、总钻风、凌瞳、OpenART mini）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>主板2.00寸IPS PRO显示例程</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -517,18 +513,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>这个例程演示主板上CCD接口驱动红孩儿并通过串口发送到上位机(逐飞助手)显示图像</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下面是每一个例程功能的说明，文件名称使用英文是因为部分IDE软件不支持中文路径</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E8_07_tsl1401_uart_seekfree_assistant_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>这个例程演示主板上显示屏接口驱动2.00寸IPS PRO显示标签控件</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -569,7 +557,410 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E2_01absolute_encoder_demo</t>
+    <t>E4_03_imu963ra_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E4_04_imu660rc_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E4_01_imu660ra_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E2_01_encoder_quadrature_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E2_02_encoder_dir_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E2_03_absolute_encoder_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主板增量式方向编码器器采集例程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主板角度编码器采集例程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主板增量式正交编码器器采集例程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板角度编码器接口初始化与角度编码器采集测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上陀螺仪接口驱动IMU660RA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E4_02_imu660rb_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上陀螺仪接口驱动IMU660RB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主板IMU660RC例程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这个例程演示主板上陀螺仪接口驱动IMU660RC，支持直接输出四元数、欧拉角</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>这个例程演示主板上CCD接口驱动红孩儿并通过串口发送到上位机(逐飞助手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Light"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>V2)显示图像</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>E8_camera（小</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钻风</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>总钻风</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>、凌瞳、OpenART mini、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>GS08RA</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>E8_0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Light"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>_tsl1401_uart_seekfree_assistant_demo</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>E08_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>传</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>感器模</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>块</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>部分</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E8_02_GS08RA_uart_seekfree_assistant_demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>个例程演示主板上灰度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>传感器</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>接口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>驱动GS08RA模块</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>并通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>串口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>送到上位机(逐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>飞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>助手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="思源黑体 CN Light"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>V2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>显</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数据</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -580,11 +971,31 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>GS08RA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS PGothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>+上位机</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
         <rFont val="微软雅黑"/>
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>角度编码</t>
+      <t>显</t>
     </r>
     <r>
       <rPr>
@@ -594,218 +1005,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>器采集例程</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS PGothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>个例程演示主板角度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>编码</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS PGothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>器接口初始化与角度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>编码</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS PGothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>器采集</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>测试</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E4_03_imu963ra_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E4_01_imu660rb_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>E4_02_imu660ra_demo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS PGothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>个例程演示主板上陀螺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>仪</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS PGothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>接口</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>驱动</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS PGothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>IMU660RB</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS PGothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>个例程演示主板上陀螺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>仪</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS PGothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>接口</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>驱动</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS PGothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>IMU660RA</t>
+      <t>示例程</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -814,7 +1014,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -869,6 +1069,36 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="思源黑体 CN Light"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
@@ -879,13 +1109,6 @@
       <name val="MS PGothic"/>
       <family val="2"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="思源黑体 CN Light"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1049,7 +1272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1073,8 +1296,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1132,9 +1354,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1172,9 +1394,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1207,26 +1429,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1259,26 +1464,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1452,7 +1640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="51.375" style="1" customWidth="1"/>
@@ -1463,25 +1651,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="27"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="26"/>
     </row>
     <row r="2" spans="1:4" ht="17.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="31"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="30"/>
     </row>
     <row r="3" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A3" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="34"/>
+      <c r="A3" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="33"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2"/>
@@ -1489,11 +1677,11 @@
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:4" ht="18" thickBot="1">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
     </row>
     <row r="6" spans="1:4" ht="14.25" thickBot="1">
       <c r="A6" s="12" t="s">
@@ -1517,7 +1705,7 @@
         <v>35</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>36</v>
@@ -1545,10 +1733,10 @@
         <v>35</v>
       </c>
       <c r="C9" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="15" t="s">
         <v>81</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="14.25" thickBot="1">
@@ -1559,7 +1747,7 @@
         <v>35</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>42</v>
@@ -1595,7 +1783,7 @@
     </row>
     <row r="13" spans="1:4" ht="14.25" thickBot="1">
       <c r="A13" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>35</v>
@@ -1650,11 +1838,11 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" thickBot="1">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
     </row>
     <row r="19" spans="1:4" ht="14.25" thickBot="1">
       <c r="A19" s="16" t="s">
@@ -1671,15 +1859,15 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
+      <c r="A20" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
     </row>
     <row r="21" spans="1:4" ht="14.25" thickBot="1">
       <c r="A21" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>61</v>
@@ -1688,565 +1876,621 @@
         <v>14</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.25" thickBot="1">
       <c r="A22" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B22" s="18" t="s">
         <v>61</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14.25" thickBot="1">
       <c r="A23" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>61</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-    </row>
-    <row r="25" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A24" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+    </row>
+    <row r="25" spans="1:4" ht="14.25" thickBot="1">
       <c r="A25" s="10" t="s">
         <v>145</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C25" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A26" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
+      <c r="B26" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="27" spans="1:4" ht="14.25" thickBot="1">
       <c r="A27" s="10" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>16</v>
+        <v>149</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A28" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>18</v>
-      </c>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
     </row>
     <row r="29" spans="1:4" ht="14.25" thickBot="1">
       <c r="A29" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="14.25" thickBot="1">
       <c r="A30" s="18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="14.25" thickBot="1">
       <c r="A31" s="10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>101</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="14.25" thickBot="1">
       <c r="A32" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A33" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C32" s="18" t="s">
+    </row>
+    <row r="34" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A34" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D34" s="18" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A33" s="23" t="s">
+    <row r="35" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A35" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-    </row>
-    <row r="34" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A34" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="17.25" thickBot="1">
-      <c r="A35" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>152</v>
-      </c>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
     </row>
     <row r="36" spans="1:4" ht="14.25" thickBot="1">
       <c r="A36" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A37" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A38" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D38" s="10" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="23" t="s">
+    <row r="39" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A39" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-    </row>
-    <row r="38" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A38" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" s="19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A39" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A40" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>10</v>
-      </c>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
     </row>
     <row r="41" spans="1:4" ht="14.25" thickBot="1">
       <c r="A41" s="19" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C41" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A42" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A43" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A44" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D44" s="19" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A42" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A43" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A44" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="14.25" thickBot="1">
       <c r="A45" s="18" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C45" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" s="18" t="s">
         <v>71</v>
-      </c>
-      <c r="D45" s="18" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="14.25" thickBot="1">
       <c r="A46" s="10" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="14.25" thickBot="1">
       <c r="A47" s="10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="14.25" thickBot="1">
       <c r="A48" s="18" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="14.25" thickBot="1">
       <c r="A49" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="14.25" thickBot="1">
       <c r="A50" s="10" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A51" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="52" spans="1:4" ht="14.25" thickBot="1">
       <c r="A52" s="10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>7</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="14.25" thickBot="1">
       <c r="A53" s="10" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A54" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>124</v>
-      </c>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" s="22"/>
+      <c r="C54" s="22"/>
     </row>
     <row r="55" spans="1:4" ht="14.25" thickBot="1">
       <c r="A55" s="10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C55" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A56" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D55" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A56" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>86</v>
+      <c r="D56" s="10" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="14.25" thickBot="1">
       <c r="A57" s="10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>28</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="14.25" thickBot="1">
       <c r="A58" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B58" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A59" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A60" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A61" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A62" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
+    </row>
+    <row r="63" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A63" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A59" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-    </row>
-    <row r="60" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A60" s="10" t="s">
+      <c r="C63" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A64" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B64" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" thickBot="1">
+      <c r="A65" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+    </row>
+    <row r="66" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A66" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B66" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A61" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D61" s="10" t="s">
+      <c r="C66" s="18" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A62" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B62" s="23"/>
-      <c r="C62" s="23"/>
-    </row>
-    <row r="63" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A63" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="D63" s="18" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
-      <c r="A127" s="4"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="5"/>
-      <c r="D127" s="6"/>
-    </row>
-    <row r="128" spans="1:4">
-      <c r="A128" s="7"/>
-      <c r="B128" s="3"/>
-      <c r="C128" s="3"/>
-      <c r="D128" s="8"/>
-    </row>
-    <row r="129" spans="1:4" ht="14.25" thickBot="1">
-      <c r="A129" s="9"/>
-      <c r="B129" s="10"/>
-      <c r="C129" s="10"/>
-      <c r="D129" s="11"/>
+      <c r="D66" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="17.25" thickBot="1">
+      <c r="A67" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="4"/>
+      <c r="B130" s="5"/>
+      <c r="C130" s="5"/>
+      <c r="D130" s="6"/>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="7"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="8"/>
+    </row>
+    <row r="132" spans="1:4" ht="14.25" thickBot="1">
+      <c r="A132" s="9"/>
+      <c r="B132" s="10"/>
+      <c r="C132" s="10"/>
+      <c r="D132" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2255,14 +2499,14 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A54:C54"/>
     <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A65:C65"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A40:C40"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
